--- a/tests/samples/XLSX_files/extracted_pdf-expected_when_having_also_numeric_part_numbers.xlsx
+++ b/tests/samples/XLSX_files/extracted_pdf-expected_when_having_also_numeric_part_numbers.xlsx
@@ -464,10 +464,8 @@
           <t>Encl, 18.5x8.84, N4, SS, Ltch, KO,CV, SB</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
+      <c r="C2" t="n">
+        <v>178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -491,10 +489,8 @@
           <t>INSULATOR BUS-BAR 16MM M4</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>605</t>
-        </is>
+      <c r="C3" t="n">
+        <v>605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -518,10 +514,8 @@
           <t>BRACKET, MOUNTING, V-CLAMP, FD SERIES</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="C4" t="n">
+        <v>500</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -545,10 +539,8 @@
           <t>Encl, 18.5x8.84, N4, SS, Ltch, KO,Bl,BK</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="C5" t="n">
+        <v>4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -572,10 +564,8 @@
           <t>Encl, 14.12x8.84, N4, SS, Ltch, KO,CV,CB</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="C6" t="n">
+        <v>16</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -599,10 +589,8 @@
           <t>Encl, 10x10x6, 9E Series, EGS</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="C7" t="n">
+        <v>7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -626,10 +614,8 @@
           <t>PCB Cover</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="C8" t="n">
+        <v>100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -653,10 +639,8 @@
           <t>Bracket, Step, 12 Position, Neutral</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="C9" t="n">
+        <v>25</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -680,10 +664,8 @@
           <t>Bracket, Step, 14 Position, Neutral</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="C10" t="n">
+        <v>50</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -707,10 +689,8 @@
           <t>Back Panel, 17.375 x 7.75</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
+      <c r="C11" t="n">
+        <v>300</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -734,10 +714,8 @@
           <t>Bracket, Support, Fiber Drawer 2U</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1.500</t>
-        </is>
+      <c r="C12" t="n">
+        <v>1500</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -761,10 +739,8 @@
           <t>Bracket, Adapter, LC-D 12 Port 18 Series</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1.500</t>
-        </is>
+      <c r="C13" t="n">
+        <v>1500</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -788,10 +764,8 @@
           <t>Back Panel, RBD-12(10-5-15)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C14" t="n">
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -815,10 +789,8 @@
           <t>Back Panel, 6W x 5.5H, 1” Step</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
+      <c r="C15" t="n">
+        <v>300</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -842,10 +814,8 @@
           <t>Cover, Poly, Neutral, RANE-217114</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
+      <c r="C16" t="n">
+        <v>300</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -869,10 +839,8 @@
           <t>Bracket, Mounting, Universal YH/YQ-ZH/ZQ</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="C17" t="n">
+        <v>66</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -896,10 +864,8 @@
           <t>Rack Adapter Plate, 23” to 19”, 2RU</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1.500</t>
-        </is>
+      <c r="C18" t="n">
+        <v>1500</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -923,10 +889,8 @@
           <t>LED Plastic Cover</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="C19" t="n">
+        <v>200</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -950,10 +914,8 @@
           <t>Cable/Wire DC12 Rack Mount Int</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="C20" t="n">
+        <v>42</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -977,10 +939,8 @@
           <t>Harness, 3 Chan Strikesorb Alarm</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="C21" t="n">
+        <v>25</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1004,10 +964,8 @@
           <t>Busbar, Neutral, N Box GEN</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="C22" t="n">
+        <v>21</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1031,10 +989,8 @@
           <t>Busbar, Bridge, 7 Pos, 26mm Pitch, L1</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="C23" t="n">
+        <v>100</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1058,10 +1014,8 @@
           <t>Busbar, DIN, Strikesorb Neutral Mt w/Lug</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="C24" t="n">
+        <v>100</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1085,10 +1039,8 @@
           <t>Busbar, Bridge, 8 Pos, 26mm Pitch</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
+      <c r="C25" t="n">
+        <v>300</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1112,10 +1064,8 @@
           <t>Busbar, DIN, Strikesorb N Mt w/Lug,Right</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
+      <c r="C26" t="n">
+        <v>300</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1139,10 +1089,8 @@
           <t>Busbar, Return, Strikesorb 30, AL</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="C27" t="n">
+        <v>64</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1166,10 +1114,8 @@
           <t>Bus Bar, Neutral, RMx-ED</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C28" t="n">
+        <v>10</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1193,10 +1139,8 @@
           <t>INPUT FO 3U SUBRACK 19IN</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C29" t="n">
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1220,10 +1164,8 @@
           <t>FO 3U SPLITTER SUBRACK</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C30" t="n">
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
